--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0003T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.74199949940573</v>
+        <v>7.758074918653431</v>
       </c>
       <c r="D2" t="n">
-        <v>47.66151074977209</v>
+        <v>7.744995496837965</v>
       </c>
       <c r="E2" t="n">
-        <v>17.56224000663527</v>
+        <v>2.853864001078232</v>
       </c>
       <c r="F2" t="n">
-        <v>17.4942778541824</v>
+        <v>2.842820151304639</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.0453764797649</v>
+        <v>6.344873677961796</v>
       </c>
       <c r="D3" t="n">
-        <v>38.9744165064828</v>
+        <v>6.333342682303456</v>
       </c>
       <c r="E3" t="n">
-        <v>17.56224000663527</v>
+        <v>2.853864001078232</v>
       </c>
       <c r="F3" t="n">
-        <v>17.4942778541824</v>
+        <v>2.842820151304639</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.297400770054161</v>
+        <v>1.023327625133801</v>
       </c>
       <c r="D4" t="n">
-        <v>6.321184974756302</v>
+        <v>1.027192558397899</v>
       </c>
       <c r="E4" t="n">
-        <v>17.56224000663527</v>
+        <v>2.853864001078232</v>
       </c>
       <c r="F4" t="n">
-        <v>17.4942778541824</v>
+        <v>2.842820151304639</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.46885801535467</v>
+        <v>6.088689427495134</v>
       </c>
       <c r="D5" t="n">
-        <v>37.59155839675662</v>
+        <v>6.10862823947295</v>
       </c>
       <c r="E5" t="n">
-        <v>17.56224000663527</v>
+        <v>2.853864001078232</v>
       </c>
       <c r="F5" t="n">
-        <v>17.4942778541824</v>
+        <v>2.842820151304639</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>6.280019615444887</v>
+        <v>1.020503187509794</v>
       </c>
       <c r="D6" t="n">
-        <v>6.481856348511047</v>
+        <v>1.053301656633045</v>
       </c>
       <c r="E6" t="n">
-        <v>17.56224000663527</v>
+        <v>2.853864001078232</v>
       </c>
       <c r="F6" t="n">
-        <v>17.4942778541824</v>
+        <v>2.842820151304639</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
